--- a/XLS-004 - Decision Log - v0.2.xlsx
+++ b/XLS-004 - Decision Log - v0.2.xlsx
@@ -490,7 +490,7 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PMOC Software | Fase 1 | v0.2 DRAFT | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved | Status: aguardando segunda revisão formal da Services.NET | ATENÇÃO: a aceitação da auditoria da Fase 1 NÃO converte decisões em 'Aprovada'. DEC-001 a DEC-010 permanecem 'Proposta'.</t>
+          <t>PMOC Software | Fase 1 | v0.2 — APPROVED | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved; Services.NET segunda revisão formal da Fase 1 v0.2; Services.NET segunda revisão formal da Fase 1 v0.2 | Status: APPROVED WITH OPEN ACTIONS | DEC-001 a DEC-010 permanecem 'Proposta'; somente DEC-011 está 'Aprovada'.</t>
         </is>
       </c>
     </row>
@@ -548,520 +548,520 @@
       </c>
     </row>
     <row r="5" ht="35.05" customHeight="1" s="8">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>DEC-001</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>O produto é concebido como plataforma de gestão de manutenção, ativos, operações de campo e conformidade; PMOC é o primeiro domínio regulatório atendido</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Master Specification §5</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Tratar apenas PMOC como formulário</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Services.NET</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>Define modelo de domínio e roadmap</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>DOC-001, DOC-002</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23.85" customHeight="1" s="8">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>DEC-002</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Não definir nome comercial nesta fase</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Decisão do patrocinador pendente</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>Definir nome provisório</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>Patrocinador (STK-001)</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Comunicação e identidade adiadas</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>OQ-001</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.85" customHeight="1" s="8">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>DEC-003</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Arquitetura</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Adotar Modular Monolith + API First como hipótese inicial, a confirmar por ADR</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Menor complexidade operacional inicial</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Microsserviços desde o início</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>Architect (STK-003)</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Estrutura de módulos e contratos</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>DOC-001 §26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35.05" customHeight="1" s="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>DEC-004</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Arquitetura</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Multi-tenancy obrigatória desde a concepção, como regra semântica e de segurança; o modelo físico de isolamento é definido em ADR-001</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Requisito estruturante do produto</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>Single-tenant no MVP; prescrever coluna TenantId na Fase 1</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>Architect (STK-003)</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Modelo de dados e segurança</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>ADR-001, DOC-001 §25</t>
         </is>
       </c>
     </row>
     <row r="9" ht="35.05" customHeight="1" s="8">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>DEC-005</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Conformidade</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Adotar Compliance as Data: requisitos regulatórios, periodicidades e parâmetros como dado versionado, distinguindo capacidade estrutural de conteúdo regulatório</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Legislação é mutável e sua interpretação não cabe à engenharia</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Regras no código; carregar parâmetros sem validação</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Architect (STK-003)</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>Modelo de domínio, banco e escopo do MVP</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>DOC-002 PP-02, DOC-007 §3.1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="23.85" customHeight="1" s="8">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>DEC-006</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>MVP é Web First; mobile e offline são Pós-MVP</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Cliente-piloto usará navegador</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>Mobile no MVP</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>Product Owner (STK-002)</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Escopo e cronograma</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>DOC-007</t>
         </is>
       </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="8">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>DEC-007</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Segurança</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Auditoria de negócio é requisito da primeira versão, separada de log técnico</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Rastreabilidade e defensabilidade</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Auditoria em versão futura</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>Architect (STK-003)</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>Modelo de dados e aceite</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>CAP-090, ADR-006</t>
         </is>
       </c>
     </row>
     <row r="12" ht="23.85" customHeight="1" s="8">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>DEC-008</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Governança</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Roadmap por ondas de valor, sem datas, até definição de equipe, orçamento e prazo</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Informação indisponível</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Datas estimadas</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>Patrocinador (STK-001)</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>Planejamento</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>DOC-008, OQ-007</t>
         </is>
       </c>
     </row>
     <row r="13" ht="35.05" customHeight="1" s="8">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>DEC-009</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Normas técnicas protegidas serão referenciadas, nunca reproduzidas; norma técnica não recebe status de lei por conveniência documental</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Direito autoral e precisão jurídica</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Reprodução interna; equiparar norma técnica a lei</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>Services.NET / Jurídico (STK-007)</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>Documentação e base de conformidade</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>CON-004, DOC-001 §5.2</t>
         </is>
       </c>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="8">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>DEC-010</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Governança</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Nenhum código será iniciado antes da aprovação das fases documentais e dos ADRs estruturantes</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Master Specification §1 e §26</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>Prototipar em paralelo</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>Patrocinador (STK-001)</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>Sequenciamento do projeto</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>DOC-008 W0</t>
         </is>
@@ -1085,22 +1085,22 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Definir qual será a fonte autoritativa dos artefatos de engenharia a partir da adoção do fluxo de edição local/versionamento Git, e como as cópias no Microsoft 365 serão sincronizadas ou tratadas</t>
+          <t>Microsoft 365 será o ambiente de autoria, colaboração, apresentação, visualização executiva, Word, Excel, Power BI e interação com agentes integrados ao ambiente corporativo. Git será a baseline técnica autoritativa e versionada dos artefatos de engenharia formalmente publicados/aprovados. Em caso de divergência entre cópia M365 e baseline aprovada no Git, prevalece a baseline aprovada no Git.</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>A revisão local por Codex introduz versionamento Git efetivo sobre artefatos originalmente produzidos no Microsoft 365; a autoridade documental não deve mudar silenciosamente</t>
+          <t>Decisão formal da Services.NET na segunda revisão da Fase 1 v0.2; evita fontes conflitantes e define precedência operacional entre M365 e Git.</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>A. M365 permanece autoritativo e Git é espelho; B. Git passa a ser autoritativo para artefatos de engenharia e M365 é colaboração/apresentação; C. divisão explícita por tipo de artefato</t>
+          <t>A. M365 autoritativo e Git espelho; B. Git autoritativo para artefatos de engenharia e M365 colaboração/apresentação; C. divisão explícita por tipo de artefato. A decisão aprovada combina M365 para autoria/colaboração/apresentação e Git como baseline técnica autoritativa.</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Proposta</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>Evita fontes conflitantes entre documentos Office, Markdown e histórico Git</t>
+          <t>Regra operacional: M365 → autoria/alteração → revisão → publicação → Git; ou Git → alteração técnica → revisão/aprovação → baseline → sincronização da representação M365 quando aplicável.</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>DOC-001 §30, CON-010, Overview_Project.md, PHASE-01-REVIEW</t>
+          <t>DOC-001 §30, CON-010, Overview_Project.md, PHASE-01-REVIEW, CHANGE-REPORT</t>
         </is>
       </c>
     </row>
@@ -1161,10 +1161,11 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Nenhum ADR foi decidido nesta fase. O conteúdo do ADR-008 NÃO é antecipado; apenas sua posição na sequência de dependências. | v0.2 DRAFT</t>
-        </is>
-      </c>
-    </row>
+          <t>Nenhum ADR foi decidido nesta fase. O conteúdo do ADR-008 NÃO é antecipado; apenas sua posição na sequência de dependências. | v0.2 — APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="8">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -1203,259 +1204,259 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="8">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ADR-001</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Modelo de isolamento multi-tenant</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Proposto</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Fase 5</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Todo o W1</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>DEC-004, DOC-001 §25</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23.85" customHeight="1" s="8">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>ADR-002</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Estratégia de identificadores (avaliar UUIDv7 ou equivalente)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Proposto</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Fase 5</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>W1 e W3 (offline)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>Master Spec §13</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="8">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>ADR-003</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Stack de back-end (ASP.NET Core x NestJS)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Proposto</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Fase 5</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>Master Spec §11</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>ADR-004</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Stack de front-end (React/Next.js)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Proposto</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Fase 5</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>Master Spec §11</t>
         </is>
       </c>
     </row>
     <row r="9" ht="23.85" customHeight="1" s="8">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ADR-005</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Armazenamento de evidências e documentos (Object Storage)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Proposto</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Fase 5/6</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>CAP-070 a CAP-073</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>DOC-006 D8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="8">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>ADR-006</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Modelo de auditoria de negócio</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Proposto</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Fase 6</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>CAP-090 a CAP-092</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>DEC-007</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="8">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>ADR-007</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Estratégia de versionamento de API</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Proposto</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Fase 7</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>CAP-100</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>AC-MVP-08</t>
         </is>
@@ -1512,7 +1513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="7" min="1" max="1"/>
@@ -1532,7 +1533,7 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Registro de controle de mudança da revisão corretiva. A aceitação da auditoria NÃO altera o status das decisões. | v0.2 DRAFT | 22/09/2026</t>
+          <t>Registro de controle de mudança da revisão corretiva e formalização final. A aprovação da Fase 1 NÃO altera DEC-001 a DEC-010; DEC-011 está aprovada. | v0.2 — APPROVED | 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -1570,486 +1571,486 @@
       </c>
     </row>
     <row r="5" ht="35.05" customHeight="1" s="8">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>AUDIT-01</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Auditoria técnica independente da Fase 1 (v0.1) formalmente aceita pela Services.NET</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Aceitação da auditoria como processo; NÃO constitui aprovação individual das decisões DEC-001 a DEC-010, que permanecem 'Proposta'</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Todos os artefatos da Fase 1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23.85" customHeight="1" s="8">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>CHG-01</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Incorporação da ABNT NBR 17037 à matriz regulatória preliminar, como norma técnica</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>DOC-001 §5.1 e §5.2; OQ-004; OQ-019; RSK-001; RSK-011; PHASE-01-REVIEW INC-001</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>DOC-001, XLS-002, XLS-003</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.85" customHeight="1" s="8">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>CHG-02</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Distinção conceitual entre Regra A (aplicabilidade do PMOC) e Regra B (exigência de responsável técnico)</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>DOC-001 §5.3; CAP-035; OQ-021; PHASE-01-REVIEW INC-003</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>DOC-001, DOC-006, XLS-003</t>
         </is>
       </c>
     </row>
     <row r="8" ht="23.85" customHeight="1" s="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>CHG-03</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Reformulação de OQ-012 (Portaria GM/MS nº 3.523/1998) reconhecendo evidências de aplicação atual</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>XLS-003</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>XLS-003, DOC-001</t>
         </is>
       </c>
     </row>
     <row r="9" ht="23.85" customHeight="1" s="8">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>CHG-04</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>CAP-033 separada entre capacidade estrutural (MVP) e conteúdo regulatório (não carregado sem validação)</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>DOC-006, DOC-007 §3.1, OOS-015, AC-MVP-11, RTM</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>DOC-003, DOC-006, DOC-007, XLS-005</t>
         </is>
       </c>
     </row>
     <row r="10" ht="23.85" customHeight="1" s="8">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>CHG-05</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Remoção da prescrição física de coluna TenantId; mantida a regra semântica e de segurança</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>DOC-001 §25, PE-02, NFR-MVP-01, DATA-001</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>DOC-001, DOC-002, DOC-007, XLS-005</t>
         </is>
       </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="8">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>CHG-06</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Harmonização do tratamento de assinatura como 'A validar', sem nível presumido</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>ASM-012, CAP-054, OOS-010, DOC-007, OQ-006</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>DOC-003, DOC-005, DOC-006, DOC-007, XLS-001, XLS-003</t>
         </is>
       </c>
     </row>
     <row r="12" ht="23.85" customHeight="1" s="8">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>CHG-07</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Reformulação de AC-MVP-03 (tipos de OS) e AC-MVP-08 (API First não literal)</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>DOC-007 §6, DOC-001 §26, CAP-045, CAP-050</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>DOC-001, DOC-006, DOC-007, XLS-005</t>
         </is>
       </c>
     </row>
     <row r="13" ht="23.85" customHeight="1" s="8">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>CHG-08</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Separação das autoridades Jurídico (STK-007) e DPO (STK-021)</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>DOC-004, RACI, XLS-001, XLS-002, XLS-003</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>DOC-001, DOC-004, XLS-001, XLS-002, XLS-003</t>
         </is>
       </c>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="8">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>CHG-09</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>ADR-008 posicionado como pré-requisito das partes dependentes do modelo de Compliance as Data</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>DOC-008 W1 e §5; ADR Register; DEP-009</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>DOC-008, XLS-001, XLS-004</t>
         </is>
       </c>
     </row>
     <row r="15" ht="23.85" customHeight="1" s="8">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>CHG-10</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Princípio PP-13 — preservação do estado de referência do PMOC emitido</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>DOC-001 §9.2, DOC-002 PP-13, CAP-037, AC-MVP-02, OQ-020, RSK-019</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>DOC-001, DOC-002, DOC-005, DOC-006, DOC-007, XLS-002, XLS-003</t>
         </is>
       </c>
     </row>
     <row r="16" ht="23.85" customHeight="1" s="8">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>CHG-11</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Correção das fórmulas de consolidação das abas Summary</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>XLS-001 (restrições e dependências contavam o cabeçalho); verificação estendida às demais planilhas</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>XLS-001, XLS-002, XLS-003</t>
         </is>
       </c>
     </row>
     <row r="17" ht="23.85" customHeight="1" s="8">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>CHG-12</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Correção da consolidação de capacidades: 79 no total e 50 no MVP (a v0.1 declarava 77 e 43)</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>DOC-006 §4; DOC-007 §3. Catálogo não foi alterado</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>DOC-001, DOC-006, DOC-007</t>
         </is>
       </c>
     </row>
     <row r="18" ht="23.85" customHeight="1" s="8">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>CHG-13</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Overview_Project.md marcado como REFERENCE / NON-AUTHORITATIVE e correção da duplicidade de AGENTS.md</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Patch entregue à parte; arquivo-fonte não disponível neste ambiente</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Overview_Project.md, DOC-001 §30, CON-010</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="8">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>CHG-14</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Services.NET Phase 1 Audit — Approved</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Padronização de terminologia oficial da Fase 1</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>DOC-003 §11; aplicada aos demais artefatos</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Todos os artefatos</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" s="8">
       <c r="A20" s="13" t="inlineStr">
         <is>
           <t>CODEX-REVIEW-01</t>
@@ -2067,17 +2068,49 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Validação e conclusão técnica local da revisão v0.2 produzida pelo Opus, com fechamento de OQ-019, reformulação de OQ-010/OQ-012/OQ-021, aplicação do Overview patch, higienização de nomes canônicos e proposta DEC-011</t>
+          <t>Validação e conclusão técnica local da revisão v0.2 produzida pelo Opus, com fechamento de OQ-019, reformulação de OQ-010/OQ-012/OQ-021, aplicação do Overview patch, higienização de nomes canônicos e criação inicial de DEC-011 como proposta (posteriormente aprovada em APPROVAL-01)</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Revisão pós-Opus executada por Codex; não inicia Fase 2 e não aprova decisões</t>
+          <t>Revisão pós-Opus executada por Codex; não iniciou Fase 2 e não aprovou decisões naquele momento</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
           <t>DOC-001, DOC-006, DOC-008, XLS-001, XLS-002, XLS-003, XLS-004, XLS-005, Overview_Project.md, PHASE-01-REVIEW, CHANGE-REPORT, DIA-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" s="8">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>APPROVAL-01</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Services.NET — segunda revisão formal da Fase 1 v0.2</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Formalização final da aprovação da Fase 1 v0.2 como APPROVED WITH OPEN ACTIONS; definição de Sponsor, Product Owner institucional, tenant-piloto e aprovação de DEC-011</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Aprovação do pacote documental como base para avanço futuro; não inicia Fase 2, não decide ADRs, não altera arquitetura, não cria requisitos e não aprova automaticamente DEC-001 a DEC-010</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>DOC-001, DOC-004, XLS-001, XLS-003, XLS-004, Overview_Project.md, PHASE-01-REVIEW, CHANGE-REPORT</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="7" min="1" max="1"/>
@@ -2116,6 +2149,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="8">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -2188,7 +2222,7 @@
     <row r="11" ht="15" customHeight="1" s="8">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Esperado — decisões após Codex</t>
+          <t>Esperado — decisões após formalização final</t>
         </is>
       </c>
       <c r="B11" s="15" t="n">
@@ -2203,6 +2237,46 @@
       </c>
       <c r="B12" s="15" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Esperado — decisões após formalização final</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Esperado — decisões Proposta</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Esperado — decisões Aprovada</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Esperado — itens de controle de mudança</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
